--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_13/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_13/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>66.61</v>
+        <v>68.84</v>
       </c>
       <c r="D2" t="n">
-        <v>17.61</v>
+        <v>17.14</v>
       </c>
       <c r="E2" t="n">
-        <v>26.43</v>
+        <v>24.9</v>
       </c>
       <c r="F2" t="n">
-        <v>45.69</v>
+        <v>47.78</v>
       </c>
       <c r="G2" t="n">
-        <v>50.94</v>
+        <v>54.49</v>
       </c>
       <c r="H2" t="n">
-        <v>61.28</v>
+        <v>64.89</v>
       </c>
       <c r="I2" t="n">
-        <v>81.37</v>
+        <v>82.72</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>54.31</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>46.78</v>
+        <v>45.58</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16</v>
+        <v>0.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2.49</v>
+        <v>0.44</v>
       </c>
       <c r="F3" t="n">
-        <v>42.79</v>
+        <v>45.5</v>
       </c>
       <c r="G3" t="n">
-        <v>46.48</v>
+        <v>45.5</v>
       </c>
       <c r="H3" t="n">
-        <v>46.52</v>
+        <v>45.5</v>
       </c>
       <c r="I3" t="n">
-        <v>47.64</v>
+        <v>45.51</v>
       </c>
       <c r="J3" t="n">
-        <v>48.22</v>
+        <v>46.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.43</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.539999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="E4" t="n">
-        <v>18.57</v>
+        <v>17.92</v>
       </c>
       <c r="F4" t="n">
-        <v>6.23</v>
+        <v>6.99</v>
       </c>
       <c r="G4" t="n">
-        <v>7.14</v>
+        <v>7.34</v>
       </c>
       <c r="H4" t="n">
-        <v>8.27</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10.28</v>
+        <v>10.68</v>
       </c>
       <c r="J4" t="n">
-        <v>11.31</v>
+        <v>11.39</v>
       </c>
       <c r="K4" t="n">
-        <v>5.09</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>129.58</v>
+        <v>87.64</v>
       </c>
       <c r="D5" t="n">
-        <v>43.96</v>
+        <v>17.9</v>
       </c>
       <c r="E5" t="n">
-        <v>33.92</v>
+        <v>20.43</v>
       </c>
       <c r="F5" t="n">
-        <v>68.88</v>
+        <v>58.55</v>
       </c>
       <c r="G5" t="n">
-        <v>97.59</v>
+        <v>69.5</v>
       </c>
       <c r="H5" t="n">
-        <v>107.16</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>183.21</v>
+        <v>103.23</v>
       </c>
       <c r="J5" t="n">
-        <v>199.71</v>
+        <v>120.72</v>
       </c>
       <c r="K5" t="n">
-        <v>130.83</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.64</v>
+        <v>3.44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>1.14</v>
       </c>
       <c r="E6" t="n">
-        <v>7.88</v>
+        <v>33.14</v>
       </c>
       <c r="F6" t="n">
-        <v>3.46</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>4.64</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>4.71</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="K6" t="n">
-        <v>1.53</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
